--- a/diseases/d174/2010-2014.xlsx
+++ b/diseases/d174/2010-2014.xlsx
@@ -4052,7 +4052,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11415,7 +11415,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12757,7 +12757,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -13954,7 +13954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14498,7 +14498,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -14897,7 +14897,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15296,7 +15296,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15695,7 +15695,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16094,7 +16094,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -16638,7 +16638,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17037,7 +17037,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17436,7 +17436,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -17835,7 +17835,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -18379,7 +18379,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -18778,7 +18778,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -19177,7 +19177,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19576,7 +19576,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -20120,7 +20120,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20519,7 +20519,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -20918,7 +20918,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -22260,7 +22260,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -22659,7 +22659,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -23457,7 +23457,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24001,7 +24001,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24400,7 +24400,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -24799,7 +24799,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -25198,7 +25198,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -25597,7 +25597,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26141,7 +26141,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -26540,7 +26540,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -26939,7 +26939,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27338,7 +27338,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -27882,7 +27882,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -28281,7 +28281,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -28680,7 +28680,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29079,7 +29079,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -29623,7 +29623,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30022,7 +30022,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -30421,7 +30421,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -30820,7 +30820,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -31219,7 +31219,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -31763,7 +31763,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -32162,7 +32162,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -32561,7 +32561,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -32960,7 +32960,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33504,7 +33504,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -33903,7 +33903,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -34302,7 +34302,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -34701,7 +34701,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -35245,7 +35245,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -35644,7 +35644,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -36043,7 +36043,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -36442,7 +36442,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -36986,7 +36986,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -37385,7 +37385,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -37784,7 +37784,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38183,7 +38183,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
@@ -38582,7 +38582,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
@@ -39126,7 +39126,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -39525,7 +39525,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -39924,7 +39924,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -40323,7 +40323,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -40867,7 +40867,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -41266,7 +41266,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -41665,7 +41665,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -42064,7 +42064,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -42463,7 +42463,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -43007,7 +43007,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -43406,7 +43406,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -43805,7 +43805,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -44204,7 +44204,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -44748,7 +44748,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -45147,7 +45147,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
@@ -45546,7 +45546,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -45945,7 +45945,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -46489,7 +46489,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -46888,7 +46888,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -47287,7 +47287,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -47686,7 +47686,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -48085,7 +48085,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -48629,7 +48629,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -49028,7 +49028,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -49427,7 +49427,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -49826,7 +49826,7 @@
       </c>
       <c r="AJ260" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK260" t="inlineStr">
@@ -50370,7 +50370,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -50769,7 +50769,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -51168,7 +51168,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -51567,7 +51567,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -52111,7 +52111,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -52510,7 +52510,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -52909,7 +52909,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -53308,7 +53308,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
@@ -53707,7 +53707,7 @@
       </c>
       <c r="AJ280" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK280" t="inlineStr">
@@ -54251,7 +54251,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -54650,7 +54650,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -55049,7 +55049,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55448,7 +55448,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">

--- a/diseases/d174/2010-2014.xlsx
+++ b/diseases/d174/2010-2014.xlsx
@@ -773,6 +773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -918,6 +923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1063,6 +1073,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1208,6 +1223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1353,6 +1373,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1498,6 +1523,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1643,6 +1673,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1788,6 +1823,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1933,6 +1973,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2078,6 +2123,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2223,6 +2273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2368,6 +2423,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2513,6 +2573,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2658,6 +2723,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2803,6 +2873,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2948,6 +3023,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3093,6 +3173,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3238,6 +3323,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3383,6 +3473,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3528,6 +3623,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3673,6 +3773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5015,6 +5120,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6756,6 +6866,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8497,6 +8612,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10637,6 +10757,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12378,6 +12503,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14119,6 +14249,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16259,6 +16394,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18000,6 +18140,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19741,6 +19886,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21881,6 +22031,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23622,6 +23777,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25762,6 +25922,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27503,6 +27668,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29244,6 +29414,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31384,6 +31559,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33125,6 +33305,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34866,6 +35051,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36607,6 +36797,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38747,6 +38942,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40488,6 +40688,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42628,6 +42833,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44369,6 +44579,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46110,6 +46325,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48250,6 +48470,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49991,6 +50216,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51732,6 +51962,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53870,6 +54105,11 @@
       <c r="S281" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO281" t="inlineStr">

--- a/diseases/d174/2010-2014.xlsx
+++ b/diseases/d174/2010-2014.xlsx
@@ -4157,7 +4157,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11540,7 +11540,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -11939,7 +11939,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12338,7 +12338,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12887,7 +12887,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -13685,7 +13685,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15032,7 +15032,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15431,7 +15431,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15830,7 +15830,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16229,7 +16229,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -16778,7 +16778,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17177,7 +17177,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -17975,7 +17975,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -18923,7 +18923,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -19322,7 +19322,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19721,7 +19721,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -20270,7 +20270,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20669,7 +20669,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21068,7 +21068,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -21467,7 +21467,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -21866,7 +21866,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -22415,7 +22415,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -23213,7 +23213,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24161,7 +24161,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24560,7 +24560,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -24959,7 +24959,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -25358,7 +25358,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -25757,7 +25757,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26306,7 +26306,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -26705,7 +26705,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27503,7 +27503,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28052,7 +28052,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -28451,7 +28451,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -28850,7 +28850,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29249,7 +29249,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -29798,7 +29798,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30197,7 +30197,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -30596,7 +30596,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -30995,7 +30995,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -31943,7 +31943,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -32342,7 +32342,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -32741,7 +32741,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -33140,7 +33140,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33689,7 +33689,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -34088,7 +34088,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -34487,7 +34487,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -34886,7 +34886,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -35435,7 +35435,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -35834,7 +35834,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -36233,7 +36233,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -36632,7 +36632,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37181,7 +37181,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -37580,7 +37580,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -37979,7 +37979,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38378,7 +38378,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
@@ -38777,7 +38777,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
@@ -39326,7 +39326,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -39725,7 +39725,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -40124,7 +40124,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -40523,7 +40523,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -41072,7 +41072,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -41471,7 +41471,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -41870,7 +41870,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -42269,7 +42269,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -42668,7 +42668,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -43217,7 +43217,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -43616,7 +43616,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -44015,7 +44015,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -44414,7 +44414,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -44963,7 +44963,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -45362,7 +45362,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
@@ -45761,7 +45761,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -46160,7 +46160,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -46709,7 +46709,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -47108,7 +47108,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -47507,7 +47507,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -47906,7 +47906,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -48305,7 +48305,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -48854,7 +48854,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -49253,7 +49253,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -49652,7 +49652,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -50051,7 +50051,7 @@
       </c>
       <c r="AJ260" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK260" t="inlineStr">
@@ -50600,7 +50600,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -50999,7 +50999,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -51398,7 +51398,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -51797,7 +51797,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -52346,7 +52346,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -52745,7 +52745,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -53144,7 +53144,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -53543,7 +53543,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
@@ -53942,7 +53942,7 @@
       </c>
       <c r="AJ280" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK280" t="inlineStr">
@@ -54491,7 +54491,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -54890,7 +54890,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -55289,7 +55289,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55688,7 +55688,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">

--- a/diseases/d174/2010-2014.xlsx
+++ b/diseases/d174/2010-2014.xlsx
@@ -768,11 +768,6 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -785,22 +780,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -918,11 +903,6 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -935,22 +915,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1068,11 +1038,6 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1085,22 +1050,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1218,11 +1173,6 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1235,22 +1185,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1368,11 +1308,6 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1385,22 +1320,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1518,11 +1443,6 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1535,22 +1455,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1668,11 +1578,6 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1685,22 +1590,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1818,11 +1713,6 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1835,22 +1725,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1968,11 +1848,6 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1985,22 +1860,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2118,11 +1983,6 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2135,22 +1995,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2268,11 +2118,6 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2285,22 +2130,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2418,11 +2253,6 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2435,22 +2265,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2568,11 +2388,6 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2585,22 +2400,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2718,11 +2523,6 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2735,22 +2535,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2868,11 +2658,6 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2885,22 +2670,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3018,11 +2793,6 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3035,22 +2805,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3168,11 +2928,6 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3185,22 +2940,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3318,11 +3063,6 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3335,22 +3075,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3468,11 +3198,6 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3485,22 +3210,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3618,11 +3333,6 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3635,22 +3345,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3768,11 +3468,6 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3785,22 +3480,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -5115,11 +4800,6 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5132,22 +4812,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -6861,11 +6531,6 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6878,22 +6543,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -8607,11 +8262,6 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8624,22 +8274,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -10752,11 +10392,6 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10769,22 +10404,12 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -12498,11 +12123,6 @@
       <c r="R67" t="n">
         <v>0</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12515,22 +12135,12 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -14244,11 +13854,6 @@
       <c r="R76" t="n">
         <v>0</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14261,22 +13866,12 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -16389,11 +15984,6 @@
       <c r="R87" t="n">
         <v>0</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16406,22 +15996,12 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -18135,11 +17715,6 @@
       <c r="R96" t="n">
         <v>0</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18152,22 +17727,12 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -19881,11 +19446,6 @@
       <c r="R105" t="n">
         <v>0</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19898,22 +19458,12 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -22026,11 +21576,6 @@
       <c r="R116" t="n">
         <v>0</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22043,22 +21588,12 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -23772,11 +23307,6 @@
       <c r="R125" t="n">
         <v>0</v>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23789,22 +23319,12 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -25917,11 +25437,6 @@
       <c r="R136" t="n">
         <v>0</v>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25934,22 +25449,12 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
         <v>0</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -27663,11 +27168,6 @@
       <c r="R145" t="n">
         <v>0</v>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27680,22 +27180,12 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
-      </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -29409,11 +28899,6 @@
       <c r="R154" t="n">
         <v>0</v>
       </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29426,22 +28911,12 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
         <v>0</v>
-      </c>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -31554,11 +31029,6 @@
       <c r="R165" t="n">
         <v>0</v>
       </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31571,22 +31041,12 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
         <v>0</v>
-      </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
@@ -33300,11 +32760,6 @@
       <c r="R174" t="n">
         <v>0</v>
       </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33317,22 +32772,12 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
         <v>0</v>
-      </c>
-      <c r="AU174" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
@@ -35046,11 +34491,6 @@
       <c r="R183" t="n">
         <v>0</v>
       </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35063,22 +34503,12 @@
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR183" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS183" t="inlineStr"/>
       <c r="AT183" t="n">
         <v>0</v>
-      </c>
-      <c r="AU183" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
@@ -36792,11 +36222,6 @@
       <c r="R192" t="n">
         <v>0</v>
       </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36809,22 +36234,12 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR192" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
         <v>0</v>
-      </c>
-      <c r="AU192" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
@@ -38937,11 +38352,6 @@
       <c r="R203" t="n">
         <v>0</v>
       </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -38954,22 +38364,12 @@
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR203" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS203" t="inlineStr"/>
       <c r="AT203" t="n">
         <v>0</v>
-      </c>
-      <c r="AU203" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
@@ -40683,11 +40083,6 @@
       <c r="R212" t="n">
         <v>0</v>
       </c>
-      <c r="S212" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -40700,22 +40095,12 @@
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR212" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS212" t="inlineStr"/>
       <c r="AT212" t="n">
         <v>0</v>
-      </c>
-      <c r="AU212" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
@@ -42828,11 +42213,6 @@
       <c r="R223" t="n">
         <v>0</v>
       </c>
-      <c r="S223" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA223" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -42845,22 +42225,12 @@
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR223" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr"/>
       <c r="AT223" t="n">
         <v>0</v>
-      </c>
-      <c r="AU223" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
@@ -44574,11 +43944,6 @@
       <c r="R232" t="n">
         <v>0</v>
       </c>
-      <c r="S232" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA232" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -44591,22 +43956,12 @@
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR232" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS232" t="inlineStr"/>
       <c r="AT232" t="n">
         <v>0</v>
-      </c>
-      <c r="AU232" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
@@ -46320,11 +45675,6 @@
       <c r="R241" t="n">
         <v>0</v>
       </c>
-      <c r="S241" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -46337,22 +45687,12 @@
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR241" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS241" t="inlineStr"/>
       <c r="AT241" t="n">
         <v>0</v>
-      </c>
-      <c r="AU241" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
@@ -48465,11 +47805,6 @@
       <c r="R252" t="n">
         <v>0</v>
       </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA252" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48482,22 +47817,12 @@
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR252" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS252" t="inlineStr"/>
       <c r="AT252" t="n">
         <v>0</v>
-      </c>
-      <c r="AU252" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
@@ -50211,11 +49536,6 @@
       <c r="R261" t="n">
         <v>0</v>
       </c>
-      <c r="S261" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA261" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50228,22 +49548,12 @@
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR261" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS261" t="inlineStr"/>
       <c r="AT261" t="n">
         <v>0</v>
-      </c>
-      <c r="AU261" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
@@ -51957,11 +51267,6 @@
       <c r="R270" t="n">
         <v>0</v>
       </c>
-      <c r="S270" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA270" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -51974,22 +51279,12 @@
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR270" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS270" t="inlineStr"/>
       <c r="AT270" t="n">
         <v>0</v>
-      </c>
-      <c r="AU270" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV270" t="inlineStr">
         <is>
@@ -54102,11 +53397,6 @@
       <c r="R281" t="n">
         <v>0</v>
       </c>
-      <c r="S281" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA281" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -54119,22 +53409,12 @@
       </c>
       <c r="AP281" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR281" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS281" t="inlineStr"/>
       <c r="AT281" t="n">
         <v>0</v>
-      </c>
-      <c r="AU281" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV281" t="inlineStr">
         <is>

--- a/diseases/d174/2010-2014.xlsx
+++ b/diseases/d174/2010-2014.xlsx
@@ -768,6 +768,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -780,12 +785,22 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -903,6 +918,11 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -915,12 +935,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1038,6 +1068,11 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1050,12 +1085,22 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1173,6 +1218,11 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1185,12 +1235,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1308,6 +1368,11 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1320,12 +1385,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1443,6 +1518,11 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1455,12 +1535,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1578,6 +1668,11 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1590,12 +1685,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1713,6 +1818,11 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1725,12 +1835,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1848,6 +1968,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1860,12 +1985,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -1983,6 +2118,11 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1995,12 +2135,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2118,6 +2268,11 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2130,12 +2285,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2253,6 +2418,11 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2265,12 +2435,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2388,6 +2568,11 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2400,12 +2585,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2523,6 +2718,11 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2535,12 +2735,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2658,6 +2868,11 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2670,12 +2885,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -2793,6 +3018,11 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2805,12 +3035,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -2928,6 +3168,11 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2940,12 +3185,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3063,6 +3318,11 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3075,12 +3335,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3198,6 +3468,11 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3210,12 +3485,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3333,6 +3618,11 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3345,12 +3635,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3468,6 +3768,11 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3480,12 +3785,22 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -4044,6 +4359,11 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4056,12 +4376,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4767,6 +5097,11 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4779,12 +5114,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5490,6 +5835,11 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5502,12 +5852,22 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6360,6 +6720,11 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6372,12 +6737,22 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7083,6 +7458,11 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7095,12 +7475,22 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7806,6 +8196,11 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7818,12 +8213,22 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8676,6 +9081,11 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8688,12 +9098,22 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9399,6 +9819,11 @@
       <c r="R63" t="n">
         <v>0</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9411,12 +9836,22 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -10122,6 +10557,11 @@
       <c r="R68" t="n">
         <v>0</v>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10134,12 +10574,22 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -10992,6 +11442,11 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11004,12 +11459,22 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11715,6 +12180,11 @@
       <c r="R79" t="n">
         <v>0</v>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11727,12 +12197,22 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -12585,6 +13065,11 @@
       <c r="R85" t="n">
         <v>0</v>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12597,12 +13082,22 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -13308,6 +13803,11 @@
       <c r="R90" t="n">
         <v>0</v>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13320,12 +13820,22 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -14031,6 +14541,11 @@
       <c r="R95" t="n">
         <v>0</v>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14043,12 +14558,22 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -14901,6 +15426,11 @@
       <c r="R101" t="n">
         <v>0</v>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14913,12 +15443,22 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -15624,6 +16164,11 @@
       <c r="R106" t="n">
         <v>0</v>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15636,12 +16181,22 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -16347,6 +16902,11 @@
       <c r="R111" t="n">
         <v>0</v>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16359,12 +16919,22 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -17070,6 +17640,11 @@
       <c r="R116" t="n">
         <v>0</v>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17082,12 +17657,22 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -17940,6 +18525,11 @@
       <c r="R122" t="n">
         <v>0</v>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17952,12 +18542,22 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -18663,6 +19263,11 @@
       <c r="R127" t="n">
         <v>0</v>
       </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18675,12 +19280,22 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -19533,6 +20148,11 @@
       <c r="R133" t="n">
         <v>0</v>
       </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19545,12 +20165,22 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
         <v>0</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -20256,6 +20886,11 @@
       <c r="R138" t="n">
         <v>0</v>
       </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20268,12 +20903,22 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
         <v>0</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -20979,6 +21624,11 @@
       <c r="R143" t="n">
         <v>0</v>
       </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20991,12 +21641,22 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
         <v>0</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -21849,6 +22509,11 @@
       <c r="R149" t="n">
         <v>0</v>
       </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21861,12 +22526,22 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
         <v>0</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -22572,6 +23247,11 @@
       <c r="R154" t="n">
         <v>0</v>
       </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22584,12 +23264,22 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
         <v>0</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -23295,6 +23985,11 @@
       <c r="R159" t="n">
         <v>0</v>
       </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23307,12 +24002,22 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
         <v>0</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
@@ -24165,6 +24870,11 @@
       <c r="R165" t="n">
         <v>0</v>
       </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24177,12 +24887,22 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
         <v>0</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
